--- a/examples/comparisons-rppa.xlsx
+++ b/examples/comparisons-rppa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanmaygandhi/Library/CloudStorage/Box-Box/runModac/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E39A418-9EC3-214D-BDCC-4B0A3299C334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB05A9AA-C36B-DF43-8900-6F14BB745012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17560" yWindow="5320" windowWidth="16040" windowHeight="15680" xr2:uid="{AC62268A-3574-A143-9B0A-533FA44997D6}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>test</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>differential_analysis_space</t>
+  </si>
+  <si>
+    <t>linear</t>
   </si>
 </sst>
 </file>
@@ -675,7 +678,7 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
